--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484069_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484069_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3124</v>
+        <v>5.2206</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9569</v>
+        <v>7.7528</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.6444</v>
+        <v>-2.5322</v>
       </c>
       <c r="G2" t="n">
         <v>5.1454</v>
@@ -610,13 +610,13 @@
         <v>1.1903</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1665</v>
+        <v>-1.2583</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5044</v>
+        <v>-0.7084</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6621</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>1.1352</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4708</v>
+        <v>2.4286</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8149</v>
+        <v>1.0813</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6559</v>
+        <v>1.3472</v>
       </c>
       <c r="G3" t="n">
         <v>3.2665</v>
@@ -688,13 +688,13 @@
         <v>0.5952</v>
       </c>
       <c r="S3" t="n">
-        <v>0.009599999999999999</v>
+        <v>-0.0326</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5498</v>
+        <v>-0.2834</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5594</v>
+        <v>0.2507</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4085</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>J. BRADLEY MAYOL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9525</v>
+        <v>1.189</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4708</v>
+        <v>0.8015</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4817</v>
+        <v>0.3876</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0179</v>
+        <v>0.9028</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6809</v>
+        <v>0.0348</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6987</v>
+        <v>0.868</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2261</v>
+        <v>1.3965</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5514</v>
+        <v>0.8266</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3253</v>
+        <v>0.5699</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2439</v>
+        <v>-0.4937</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1295</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>1.3734</v>
+        <v>0.2981</v>
       </c>
       <c r="P4" t="n">
         <v>0.7935</v>
@@ -766,19 +766,19 @@
         <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5497</v>
+        <v>-0.5073</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1054</v>
+        <v>-0.5951</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4443</v>
+        <v>0.0878</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BRADLEY MAYOL</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0411</v>
+        <v>1.0401</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5974</v>
+        <v>2.8214</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4437</v>
+        <v>-1.7812</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9028</v>
+        <v>1.1422</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0348</v>
+        <v>-1.0486</v>
       </c>
       <c r="I5" t="n">
-        <v>0.868</v>
+        <v>2.1908</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3965</v>
+        <v>3.4504</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8266</v>
+        <v>1.5577</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5699</v>
+        <v>1.8927</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4937</v>
+        <v>-2.3083</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-2.6064</v>
       </c>
       <c r="O5" t="n">
         <v>0.2981</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6553</v>
+        <v>-1.2923</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7991</v>
+        <v>-0.6291</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1439</v>
+        <v>-0.6632</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3974</v>
+        <v>0.6579</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5153</v>
+        <v>-0.4871</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1179</v>
+        <v>1.1451</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1422</v>
+        <v>0.0179</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0486</v>
+        <v>-2.6809</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1908</v>
+        <v>2.6987</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4504</v>
+        <v>-0.2261</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5577</v>
+        <v>-1.5514</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8927</v>
+        <v>1.3253</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3083</v>
+        <v>0.2439</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.6064</v>
+        <v>-1.1295</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2981</v>
+        <v>1.3734</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1903</v>
+        <v>0.7935</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.9351</v>
+        <v>0.2551</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9352</v>
+        <v>0.1475</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9999</v>
+        <v>0.1076</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>A. IDDRISU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0698</v>
+        <v>0.4993</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7198</v>
+        <v>0.8953</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6501</v>
+        <v>-0.3961</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9418</v>
+        <v>1.4237</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2772</v>
+        <v>1.0985</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6646</v>
+        <v>0.3252</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6437</v>
+        <v>0.7257</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6787</v>
+        <v>0.6855</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0351</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7018</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4015</v>
+        <v>0.413</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6997</v>
+        <v>0.2851</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2607</v>
+        <v>-0.1148</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1303</v>
+        <v>-0.0963</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1304</v>
+        <v>-0.0185</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2065</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4129</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. IDDRISU</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0365</v>
+        <v>0.1321</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6289</v>
+        <v>2.7822</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5924</v>
+        <v>-2.6501</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4237</v>
+        <v>0.9418</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0985</v>
+        <v>0.2772</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3252</v>
+        <v>0.6646</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7257</v>
+        <v>1.6437</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6855</v>
+        <v>1.6787</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>-0.0351</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6981000000000001</v>
+        <v>-0.7018</v>
       </c>
       <c r="N8" t="n">
-        <v>0.413</v>
+        <v>-1.4015</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2851</v>
+        <v>0.6997</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3968</v>
+        <v>0.5952</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5776</v>
+        <v>-0.1984</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3627</v>
+        <v>-0.0679</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2148</v>
+        <v>-0.1304</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2065</v>
       </c>
       <c r="W8" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4724</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1882</v>
+        <v>-1.076</v>
       </c>
       <c r="E9" t="n">
         <v>0.4417</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6299</v>
+        <v>-1.5177</v>
       </c>
       <c r="G9" t="n">
         <v>0.5111</v>
@@ -1156,13 +1156,13 @@
         <v>0.7935</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5009</v>
+        <v>-1.3887</v>
       </c>
       <c r="T9" t="n">
         <v>-1.1109</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.39</v>
+        <v>-0.2778</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0039</v>
+        <v>-1.8574</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0982</v>
+        <v>-2.0358</v>
       </c>
       <c r="F10" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1785</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2778</v>
@@ -1234,13 +1234,13 @@
         <v>0.5952</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3212</v>
+        <v>-1.1747</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0485</v>
+        <v>-0.9862</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2727</v>
+        <v>-0.1885</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6324</v>
+        <v>-3.4666</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1807</v>
+        <v>-0.8746</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4516</v>
+        <v>-2.5919</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5752</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4539</v>
+        <v>-1.2881</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2469</v>
+        <v>-0.9408</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.207</v>
+        <v>-0.3473</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6032</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.456000000000001</v>
+        <v>4.7676</v>
       </c>
       <c r="E12" t="n">
-        <v>12.8668</v>
+        <v>13.1787</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.410700000000002</v>
+        <v>-8.410799999999998</v>
       </c>
       <c r="G12" t="n">
         <v>10.4984</v>
@@ -1390,13 +1390,13 @@
         <v>7.9354</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.311900000000001</v>
+        <v>-7.0001</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.582400000000001</v>
+        <v>-5.270600000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7293</v>
+        <v>-1.7295</v>
       </c>
       <c r="V12" t="n">
         <v>-2.698</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. MARTIN MONZON</t>
+          <t>H. RAMON AÑIBARRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.957</v>
+        <v>5.7418</v>
       </c>
       <c r="E13" t="n">
-        <v>4.6423</v>
+        <v>7.5497</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3147</v>
+        <v>-1.8079</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8745000000000001</v>
+        <v>5.2875</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9614</v>
+        <v>0.2065</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0869</v>
+        <v>5.081</v>
       </c>
       <c r="J13" t="n">
-        <v>4.3713</v>
+        <v>7.986</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9661</v>
+        <v>2.6719</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5948</v>
+        <v>5.3141</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.4968</v>
+        <v>-2.6985</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.0047</v>
+        <v>-2.4654</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4921</v>
+        <v>-0.2331</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3968</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R13" t="n">
         <v>0.7935</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3323</v>
+        <v>1.1847</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0112</v>
+        <v>0.5556</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3435</v>
+        <v>0.6291</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1469</v>
+        <v>-0.532</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6745</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. RAMON AÑIBARRO</t>
+          <t>J. MARTIN MONZON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7386</v>
+        <v>4.5957</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2436</v>
+        <v>4.8463</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.505</v>
+        <v>-0.2506</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2875</v>
+        <v>0.8745000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2065</v>
+        <v>1.9614</v>
       </c>
       <c r="I14" t="n">
-        <v>5.081</v>
+        <v>-1.0869</v>
       </c>
       <c r="J14" t="n">
-        <v>7.986</v>
+        <v>4.3713</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6719</v>
+        <v>4.9661</v>
       </c>
       <c r="L14" t="n">
-        <v>5.3141</v>
+        <v>-0.5948</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.6985</v>
+        <v>-3.4968</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.4654</v>
+        <v>-3.0047</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2331</v>
+        <v>-0.4921</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1984</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R14" t="n">
         <v>0.7935</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1814</v>
+        <v>1.9711</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2495</v>
+        <v>0.1929</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.06809999999999999</v>
+        <v>1.7782</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.532</v>
+        <v>2.1469</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.4724</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.532</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3272</v>
+        <v>1.8326</v>
       </c>
       <c r="E15" t="n">
-        <v>7.0872</v>
+        <v>4.5364</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.76</v>
+        <v>-2.7038</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8326</v>
@@ -1624,13 +1624,13 @@
         <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>4.6514</v>
+        <v>2.1568</v>
       </c>
       <c r="T15" t="n">
-        <v>4.0246</v>
+        <v>1.4738</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6268</v>
+        <v>0.6829</v>
       </c>
       <c r="V15" t="n">
         <v>3.0874</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. GUASCH BENLLOCH</t>
+          <t>D. COFFIE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.6156</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6178</v>
+        <v>0.6355</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0187</v>
+        <v>-0.02</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2721</v>
+        <v>-0.1935</v>
       </c>
       <c r="H16" t="n">
-        <v>0.136</v>
+        <v>0.1057</v>
       </c>
       <c r="I16" t="n">
-        <v>0.136</v>
+        <v>-0.2992</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.7885</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.7057</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.0829</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2721</v>
+        <v>-0.9821</v>
       </c>
       <c r="N16" t="n">
-        <v>0.136</v>
+        <v>-0.6</v>
       </c>
       <c r="O16" t="n">
-        <v>0.136</v>
+        <v>-0.3821</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.1984</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3645</v>
+        <v>0.6107</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6178</v>
+        <v>-0.153</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2534</v>
+        <v>0.7637</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. COFFIE</t>
+          <t>P. GUASCH BENLLOCH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0127</v>
+        <v>0.2565</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2274</v>
+        <v>0.2097</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2402</v>
+        <v>0.0468</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1935</v>
+        <v>0.2721</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1057</v>
+        <v>0.136</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2992</v>
+        <v>0.136</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7885</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7057</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0829</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9821</v>
+        <v>0.2721</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6</v>
+        <v>0.136</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3821</v>
+        <v>0.136</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0176</v>
+        <v>-0.0156</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5611</v>
+        <v>0.2097</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5435</v>
+        <v>-0.2253</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5596</v>
+        <v>-0.4158</v>
       </c>
       <c r="E19" t="n">
-        <v>0.596</v>
+        <v>0.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1555</v>
+        <v>-1.2159</v>
       </c>
       <c r="G19" t="n">
         <v>-1.8606</v>
@@ -1936,13 +1936,13 @@
         <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9006</v>
+        <v>1.0444</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0056</v>
+        <v>0.1985</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9062</v>
+        <v>0.8459</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1947</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2001</v>
+        <v>-1.0157</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.074</v>
+        <v>-0.0537</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1261</v>
+        <v>-0.962</v>
       </c>
       <c r="G20" t="n">
         <v>-2.5928</v>
@@ -2014,13 +2014,13 @@
         <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.004</v>
+        <v>1.1804</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.0228</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9935</v>
+        <v>1.1576</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9431</v>
+        <v>-3.3564</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3238</v>
+        <v>-1.0177</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6193</v>
+        <v>-2.3388</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1528</v>
@@ -2170,13 +2170,13 @@
         <v>0.1984</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7822</v>
+        <v>-0.1955</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4874</v>
+        <v>-0.1813</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2948</v>
+        <v>-0.0142</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.070399999999999</v>
+        <v>-8.7005</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.4333</v>
+        <v>-6.9231</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6371</v>
+        <v>-1.7774</v>
       </c>
       <c r="G23" t="n">
         <v>-5.8914</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3259</v>
+        <v>0.0439</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7991</v>
+        <v>-0.289</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4732</v>
+        <v>0.3329</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8692</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.456099999999999</v>
+        <v>-3.775800000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>8.410599999999995</v>
+        <v>8.410500000000003</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.8668</v>
+        <v>-12.1866</v>
       </c>
       <c r="G24" t="n">
         <v>-10.4981</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.7288</v>
+        <v>-3.728800000000001</v>
       </c>
       <c r="I24" t="n">
         <v>-6.769599999999999</v>
@@ -2326,13 +2326,13 @@
         <v>3.9677</v>
       </c>
       <c r="S24" t="n">
-        <v>7.311800000000001</v>
+        <v>7.9922</v>
       </c>
       <c r="T24" t="n">
         <v>1.7296</v>
       </c>
       <c r="U24" t="n">
-        <v>5.582100000000001</v>
+        <v>6.262500000000001</v>
       </c>
       <c r="V24" t="n">
         <v>2.6979</v>
